--- a/Mouse brain RNAseq/sig_diff_splicing_events.xlsx
+++ b/Mouse brain RNAseq/sig_diff_splicing_events.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -476,30 +476,35 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>novel_splice_site</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>avg_RC_1</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>avg_RC_2</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_psi_vals_1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>mean_psi_vals_2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>sig</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>splicing_event_type</t>
         </is>
@@ -595,24 +600,27 @@
       <c r="W2">
         <v>0.353</v>
       </c>
-      <c r="X2">
+      <c r="X2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y2">
         <v>15.75</v>
       </c>
-      <c r="Y2">
+      <c r="Z2">
         <v>33.33333333333334</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>0.9775</v>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <v>0.6246666666666667</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>A5SS</t>
         </is>
@@ -708,24 +716,27 @@
       <c r="W3">
         <v>-0.654</v>
       </c>
-      <c r="X3">
+      <c r="X3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y3">
         <v>5.75</v>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <v>5.666666666666667</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>0.25075</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>0.9046666666666666</v>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>A5SS</t>
         </is>
@@ -821,24 +832,27 @@
       <c r="W4">
         <v>0.488</v>
       </c>
-      <c r="X4">
+      <c r="X4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y4">
         <v>24.75</v>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <v>34</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>0.95225</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>0.4646666666666667</v>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>A5SS</t>
         </is>
@@ -934,24 +948,27 @@
       <c r="W5">
         <v>-0.713</v>
       </c>
-      <c r="X5">
+      <c r="X5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y5">
         <v>6.25</v>
       </c>
-      <c r="Y5">
+      <c r="Z5">
         <v>8</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>0.2875</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>1</v>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>A5SS</t>
         </is>
@@ -1047,24 +1064,27 @@
       <c r="W6">
         <v>-0.546</v>
       </c>
-      <c r="X6">
+      <c r="X6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y6">
         <v>33</v>
       </c>
-      <c r="Y6">
+      <c r="Z6">
         <v>14.33333333333333</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>0.45375</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>1</v>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>A5SS</t>
         </is>
@@ -1077,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1198,30 +1218,35 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>novel_splice_site</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>avg_RC_1</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>avg_RC_2</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_psi_vals_1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>mean_psi_vals_2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>sig</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>splicing_event_type</t>
         </is>
@@ -1317,24 +1342,27 @@
       <c r="W2">
         <v>0.582</v>
       </c>
-      <c r="X2">
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2">
         <v>5.25</v>
       </c>
-      <c r="Y2">
+      <c r="Z2">
         <v>8.666666666666666</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>0.88825</v>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <v>0.3063333333333333</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>A3SS</t>
         </is>
@@ -1430,24 +1458,27 @@
       <c r="W3">
         <v>0.394</v>
       </c>
-      <c r="X3">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3">
         <v>16.5</v>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <v>21.66666666666667</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>0.92975</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>0.536</v>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>A3SS</t>
         </is>
@@ -1543,24 +1574,27 @@
       <c r="W4">
         <v>0.322</v>
       </c>
-      <c r="X4">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4">
         <v>2099.75</v>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <v>1535.666666666667</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>0.634</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>0.312</v>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>A3SS</t>
         </is>
@@ -1656,24 +1690,27 @@
       <c r="W5">
         <v>-0.397</v>
       </c>
-      <c r="X5">
+      <c r="X5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y5">
         <v>18.5</v>
       </c>
-      <c r="Y5">
+      <c r="Z5">
         <v>12.33333333333333</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>0.6025</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>1</v>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>A3SS</t>
         </is>
@@ -1769,24 +1806,27 @@
       <c r="W6">
         <v>0.631</v>
       </c>
-      <c r="X6">
+      <c r="X6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y6">
         <v>7</v>
       </c>
-      <c r="Y6">
+      <c r="Z6">
         <v>7.666666666666667</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>0.9035</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>0.2726666666666667</v>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>A3SS</t>
         </is>
@@ -1882,24 +1922,27 @@
       <c r="W7">
         <v>-0.6830000000000001</v>
       </c>
-      <c r="X7">
+      <c r="X7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y7">
         <v>10</v>
       </c>
-      <c r="Y7">
+      <c r="Z7">
         <v>12</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>0.18775</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>0.8703333333333333</v>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>A3SS</t>
         </is>
@@ -1912,7 +1955,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2043,30 +2086,35 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>novel_splice_site</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>avg_RC_1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>avg_RC_2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mean_psi_vals_1</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mean_psi_vals_2</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>sig</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>splicing_event_type</t>
         </is>
@@ -2079,7 +2127,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2200,30 +2248,35 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>novel_splice_site</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>avg_RC_1</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>avg_RC_2</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_psi_vals_1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>mean_psi_vals_2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>sig</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>splicing_event_type</t>
         </is>
@@ -2319,24 +2372,27 @@
       <c r="W2">
         <v>0.695</v>
       </c>
-      <c r="X2">
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2">
         <v>14.75</v>
       </c>
-      <c r="Y2">
+      <c r="Z2">
         <v>6.666666666666667</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>0.731</v>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <v>0.03633333333333333</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -2432,24 +2488,27 @@
       <c r="W3">
         <v>0.631</v>
       </c>
-      <c r="X3">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3">
         <v>18.75</v>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <v>22</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>0.9390000000000001</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>0.3083333333333333</v>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -2545,24 +2604,27 @@
       <c r="W4">
         <v>-0.535</v>
       </c>
-      <c r="X4">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4">
         <v>10.75</v>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <v>7</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>0.39175</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>0.9266666666666666</v>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -2658,24 +2720,27 @@
       <c r="W5">
         <v>0.6929999999999999</v>
       </c>
-      <c r="X5">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5">
         <v>12.25</v>
       </c>
-      <c r="Y5">
+      <c r="Z5">
         <v>6.333333333333333</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>0.7285</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>0.036</v>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -2771,24 +2836,27 @@
       <c r="W6">
         <v>0.328</v>
       </c>
-      <c r="X6">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6">
         <v>4871</v>
       </c>
-      <c r="Y6">
+      <c r="Z6">
         <v>3005.666666666667</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>0.712</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>0.3836666666666667</v>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -2884,24 +2952,27 @@
       <c r="W7">
         <v>0.347</v>
       </c>
-      <c r="X7">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7">
         <v>321.75</v>
       </c>
-      <c r="Y7">
+      <c r="Z7">
         <v>218</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>0.7215</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>0.3743333333333334</v>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -2997,24 +3068,27 @@
       <c r="W8">
         <v>0.33</v>
       </c>
-      <c r="X8">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8">
         <v>16.75</v>
       </c>
-      <c r="Y8">
+      <c r="Z8">
         <v>7.333333333333333</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>0.3385</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>0.008333333333333335</v>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -3110,24 +3184,27 @@
       <c r="W9">
         <v>0.554</v>
       </c>
-      <c r="X9">
+      <c r="X9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y9">
         <v>5.25</v>
       </c>
-      <c r="Y9">
+      <c r="Z9">
         <v>7.333333333333333</v>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <v>0.78875</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>0.2343333333333333</v>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -3223,24 +3300,27 @@
       <c r="W10">
         <v>-0.443</v>
       </c>
-      <c r="X10">
+      <c r="X10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y10">
         <v>25</v>
       </c>
-      <c r="Y10">
+      <c r="Z10">
         <v>17.33333333333333</v>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <v>0.55725</v>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <v>1</v>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -3336,24 +3416,27 @@
       <c r="W11">
         <v>-0.337</v>
       </c>
-      <c r="X11">
+      <c r="X11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y11">
         <v>30.75</v>
       </c>
-      <c r="Y11">
+      <c r="Z11">
         <v>20.66666666666667</v>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <v>0.66325</v>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <v>1</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -3449,24 +3532,27 @@
       <c r="W12">
         <v>-0.63</v>
       </c>
-      <c r="X12">
+      <c r="X12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y12">
         <v>7.5</v>
       </c>
-      <c r="Y12">
+      <c r="Z12">
         <v>11.66666666666667</v>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <v>0.3095</v>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -3562,24 +3648,27 @@
       <c r="W13">
         <v>0.433</v>
       </c>
-      <c r="X13">
+      <c r="X13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y13">
         <v>8.25</v>
       </c>
-      <c r="Y13">
+      <c r="Z13">
         <v>21.66666666666667</v>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <v>0.89325</v>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <v>0.4603333333333333</v>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -3675,24 +3764,27 @@
       <c r="W14">
         <v>0.579</v>
       </c>
-      <c r="X14">
+      <c r="X14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y14">
         <v>18.75</v>
       </c>
-      <c r="Y14">
+      <c r="Z14">
         <v>26.66666666666667</v>
       </c>
-      <c r="Z14">
+      <c r="AA14">
         <v>1</v>
       </c>
-      <c r="AA14">
+      <c r="AB14">
         <v>0.421</v>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -3788,24 +3880,27 @@
       <c r="W15">
         <v>0.751</v>
       </c>
-      <c r="X15">
+      <c r="X15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y15">
         <v>8.5</v>
       </c>
-      <c r="Y15">
+      <c r="Z15">
         <v>7.333333333333333</v>
       </c>
-      <c r="Z15">
+      <c r="AA15">
         <v>1</v>
       </c>
-      <c r="AA15">
+      <c r="AB15">
         <v>0.2486666666666667</v>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -3901,24 +3996,27 @@
       <c r="W16">
         <v>0.8110000000000001</v>
       </c>
-      <c r="X16">
+      <c r="X16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y16">
         <v>10.5</v>
       </c>
-      <c r="Y16">
+      <c r="Z16">
         <v>6.333333333333333</v>
       </c>
-      <c r="Z16">
+      <c r="AA16">
         <v>1</v>
       </c>
-      <c r="AA16">
+      <c r="AB16">
         <v>0.1893333333333333</v>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -4014,24 +4112,27 @@
       <c r="W17">
         <v>0.5639999999999999</v>
       </c>
-      <c r="X17">
+      <c r="X17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y17">
         <v>10.25</v>
       </c>
-      <c r="Y17">
+      <c r="Z17">
         <v>12</v>
       </c>
-      <c r="Z17">
+      <c r="AA17">
         <v>0.90625</v>
       </c>
-      <c r="AA17">
+      <c r="AB17">
         <v>0.342</v>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -4127,24 +4228,27 @@
       <c r="W18">
         <v>0.649</v>
       </c>
-      <c r="X18">
+      <c r="X18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y18">
         <v>15.25</v>
       </c>
-      <c r="Y18">
+      <c r="Z18">
         <v>7</v>
       </c>
-      <c r="Z18">
+      <c r="AA18">
         <v>0.8385</v>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <v>0.1896666666666667</v>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -4240,24 +4344,27 @@
       <c r="W19">
         <v>0.61</v>
       </c>
-      <c r="X19">
+      <c r="X19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y19">
         <v>18.75</v>
       </c>
-      <c r="Y19">
+      <c r="Z19">
         <v>19</v>
       </c>
-      <c r="Z19">
+      <c r="AA19">
         <v>0.82575</v>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <v>0.2153333333333333</v>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
@@ -4270,7 +4377,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AD16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4391,30 +4498,35 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>novel_splice_site</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>avg_RC_1</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>avg_RC_2</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_psi_vals_1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>mean_psi_vals_2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>sig</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>splicing_event_type</t>
         </is>
@@ -4510,24 +4622,27 @@
       <c r="W2">
         <v>0.415</v>
       </c>
-      <c r="X2">
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2">
         <v>8.25</v>
       </c>
-      <c r="Y2">
+      <c r="Z2">
         <v>17.33333333333333</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>0.93825</v>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <v>0.523</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -4623,24 +4738,27 @@
       <c r="W3">
         <v>0.578</v>
       </c>
-      <c r="X3">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3">
         <v>5.75</v>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <v>8.666666666666666</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>0.92375</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>0.346</v>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -4736,24 +4854,27 @@
       <c r="W4">
         <v>0.332</v>
       </c>
-      <c r="X4">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4">
         <v>15</v>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <v>22.33333333333333</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>0.9405</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>0.6083333333333334</v>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -4849,24 +4970,27 @@
       <c r="W5">
         <v>0.485</v>
       </c>
-      <c r="X5">
-        <v>12</v>
+      <c r="X5" t="b">
+        <v>0</v>
       </c>
       <c r="Y5">
         <v>12</v>
       </c>
       <c r="Z5">
+        <v>12</v>
+      </c>
+      <c r="AA5">
         <v>0.9</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>0.4146666666666667</v>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -4962,24 +5086,27 @@
       <c r="W6">
         <v>-0.873</v>
       </c>
-      <c r="X6">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6">
         <v>5.25</v>
       </c>
-      <c r="Y6">
+      <c r="Z6">
         <v>5.333333333333333</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>0.127</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>1</v>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -5075,24 +5202,27 @@
       <c r="W7">
         <v>0.512</v>
       </c>
-      <c r="X7">
+      <c r="X7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y7">
         <v>7.25</v>
       </c>
-      <c r="Y7">
+      <c r="Z7">
         <v>11.66666666666667</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>0.853</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>0.3413333333333333</v>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -5188,24 +5318,27 @@
       <c r="W8">
         <v>0.822</v>
       </c>
-      <c r="X8">
+      <c r="X8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y8">
         <v>11.25</v>
       </c>
-      <c r="Y8">
+      <c r="Z8">
         <v>9.666666666666666</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>0.91325</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>0.091</v>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -5301,24 +5434,27 @@
       <c r="W9">
         <v>0.521</v>
       </c>
-      <c r="X9">
+      <c r="X9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y9">
         <v>16.5</v>
       </c>
-      <c r="Y9">
+      <c r="Z9">
         <v>26</v>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <v>0.944</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>0.4233333333333333</v>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -5414,24 +5550,27 @@
       <c r="W10">
         <v>-0.509</v>
       </c>
-      <c r="X10">
+      <c r="X10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y10">
         <v>11</v>
       </c>
-      <c r="Y10">
+      <c r="Z10">
         <v>6.333333333333333</v>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <v>0.4075</v>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <v>0.917</v>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -5527,24 +5666,27 @@
       <c r="W11">
         <v>-0.456</v>
       </c>
-      <c r="X11">
+      <c r="X11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y11">
         <v>13</v>
       </c>
-      <c r="Y11">
+      <c r="Z11">
         <v>7.666666666666667</v>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <v>0.49075</v>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <v>0.947</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -5640,24 +5782,27 @@
       <c r="W12">
         <v>0.345</v>
       </c>
-      <c r="X12">
+      <c r="X12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y12">
         <v>1239.75</v>
       </c>
-      <c r="Y12">
+      <c r="Z12">
         <v>940</v>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <v>0.59275</v>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <v>0.248</v>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -5753,24 +5898,27 @@
       <c r="W13">
         <v>-0.501</v>
       </c>
-      <c r="X13">
+      <c r="X13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y13">
         <v>5.5</v>
       </c>
-      <c r="Y13">
+      <c r="Z13">
         <v>5</v>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <v>0.41125</v>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <v>0.9126666666666666</v>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -5866,24 +6014,27 @@
       <c r="W14">
         <v>0.517</v>
       </c>
-      <c r="X14">
+      <c r="X14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y14">
         <v>18.25</v>
       </c>
-      <c r="Y14">
+      <c r="Z14">
         <v>18.66666666666667</v>
       </c>
-      <c r="Z14">
+      <c r="AA14">
         <v>0.90625</v>
       </c>
-      <c r="AA14">
+      <c r="AB14">
         <v>0.389</v>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -5979,24 +6130,27 @@
       <c r="W15">
         <v>-0.823</v>
       </c>
-      <c r="X15">
-        <v>5</v>
+      <c r="X15" t="b">
+        <v>1</v>
       </c>
       <c r="Y15">
         <v>5</v>
       </c>
       <c r="Z15">
+        <v>5</v>
+      </c>
+      <c r="AA15">
         <v>0.1775</v>
       </c>
-      <c r="AA15">
+      <c r="AB15">
         <v>1</v>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>Up in TMAO</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -6092,24 +6246,27 @@
       <c r="W16">
         <v>0.391</v>
       </c>
-      <c r="X16">
+      <c r="X16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y16">
         <v>15.25</v>
       </c>
-      <c r="Y16">
+      <c r="Z16">
         <v>15.33333333333333</v>
       </c>
-      <c r="Z16">
+      <c r="AA16">
         <v>0.40975</v>
       </c>
-      <c r="AA16">
+      <c r="AB16">
         <v>0.01866666666666666</v>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>Up in Saline</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
